--- a/reports/Debug-snowbowl-20260106/Month to Date (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260106/Month to Date (Actual)_Revenue.xlsx
@@ -55,19 +55,19 @@
     <t>account</t>
   </si>
   <si>
+    <t xml:space="preserve">                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T101                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T104                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
   </si>
   <si>
     <t xml:space="preserve">T100                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T101                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T104                     </t>
   </si>
   <si>
     <t>department</t>
@@ -502,7 +502,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="2">
-        <v>76944.8500</v>
+        <v>-15.0000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -516,7 +516,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="2">
-        <v>1005329.2200</v>
+        <v>9.3500</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -530,7 +530,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="2">
-        <v>-15.0000</v>
+        <v>15.0000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -544,7 +544,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>9.3500</v>
+        <v>76944.8500</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -558,7 +558,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>15.0000</v>
+        <v>1005329.2200</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -642,7 +642,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="2">
-        <v>144890.1000</v>
+        <v>144911.6000</v>
       </c>
     </row>
     <row r="14" spans="1:4">
